--- a/SGC-CKN/Excel/6715dc33-90aa-4aee-8d9b-7a232d07818b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P17-154_D800_11-05-2026.xlsx
+++ b/SGC-CKN/Excel/6715dc33-90aa-4aee-8d9b-7a232d07818b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P17-154_D800_11-05-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>Dự án</t>
   </si>
@@ -220,10 +220,6 @@
   </si>
   <si>
     <t>Cuội đa màu sắc TT rất chặt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:50
-11/05/2026</t>
   </si>
   <si>
     <t xml:space="preserve">08:20
@@ -1557,10 +1553,10 @@
         <v>63</v>
       </c>
       <c r="D20" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="E20" s="37" t="s">
         <v>64</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>65</v>
       </c>
       <c r="F20" s="35">
         <v>-42.37</v>
@@ -1569,13 +1565,13 @@
         <v>-43.57</v>
       </c>
       <c r="H20" s="35">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="I20" s="35">
         <v>1.2</v>
       </c>
       <c r="J20" s="12">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="K20" s="36" t="s">
         <v>30</v>
@@ -1583,7 +1579,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1689,31 +1685,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1997,18 +1993,18 @@
         <v>-43.57</v>
       </c>
       <c r="G11" s="35">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="H11" s="35">
         <v>1.2</v>
       </c>
       <c r="I11" s="12">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B12" s="40" t="s">
         <v>30</v>
@@ -2026,13 +2022,13 @@
         <v>-43.57</v>
       </c>
       <c r="G12" s="40">
-        <v>12.65</v>
+        <v>12.98</v>
       </c>
       <c r="H12" s="40">
         <v>43.57</v>
       </c>
       <c r="I12" s="40">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/6715dc33-90aa-4aee-8d9b-7a232d07818b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P17-154_D800_11-05-2026.xlsx
+++ b/SGC-CKN/Excel/6715dc33-90aa-4aee-8d9b-7a232d07818b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P17-154_D800_11-05-2026.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="74">
   <si>
     <t>Dự án</t>
   </si>
   <si>
-    <t>Dự án số 1 khu đô thị trung tâm thành phố Thanh Hóa (Vinhomes Star City)</t>
+    <t>Star City Thanh Hóa</t>
   </si>
   <si>
     <t>Hạng mục</t>
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>19:00 10/05/2026</t>
+    <t>19:00 10/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>08:20 11/05/2026</t>
+    <t>08:20 11/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">19:09
-10/05/2026</t>
+10/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">19:58
-10/05/2026</t>
+10/03/2026</t>
   </si>
   <si>
     <t/>
@@ -112,15 +112,15 @@
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha xám ghi, xám nâu, xám vàng TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">20:00
-10/05/2026</t>
+10/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">20:58
-10/05/2026</t>
+10/03/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -130,11 +130,11 @@
   </si>
   <si>
     <t xml:space="preserve">21:00
-10/05/2026</t>
+10/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">22:27
-10/05/2026</t>
+10/03/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -144,11 +144,11 @@
   </si>
   <si>
     <t xml:space="preserve">22:30
-10/05/2026</t>
+10/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">22:58
-10/05/2026</t>
+10/03/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -158,11 +158,11 @@
   </si>
   <si>
     <t xml:space="preserve">23:00
-10/05/2026</t>
+10/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">03:59
-11/05/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -172,45 +172,42 @@
   </si>
   <si>
     <t xml:space="preserve">04:00
-11/05/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">05:20
-11/05/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">06:00
-11/05/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xám, xám vàng, xám xanh TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">06:53
-11/05/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">06:55
-11/05/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">07:30
-11/05/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>NT khoan sỏi</t>
@@ -223,7 +220,7 @@
   </si>
   <si>
     <t xml:space="preserve">08:20
-11/05/2026</t>
+11/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
@@ -1515,13 +1512,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="D19" s="34" t="s">
+      <c r="E19" s="34" t="s">
         <v>59</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>60</v>
       </c>
       <c r="F19" s="32">
         <v>-37.97</v>
@@ -1539,24 +1536,24 @@
         <v>7.54</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B20" s="35" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="E20" s="37" t="s">
         <v>63</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>60</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>64</v>
       </c>
       <c r="F20" s="35">
         <v>-42.37</v>
@@ -1579,7 +1576,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1685,31 +1682,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1952,7 +1949,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D10" s="32">
         <v>1</v>
@@ -1981,7 +1978,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" s="35">
         <v>1</v>
@@ -2004,7 +2001,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B12" s="40" t="s">
         <v>30</v>

--- a/SGC-CKN/Excel/6715dc33-90aa-4aee-8d9b-7a232d07818b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P17-154_D800_11-05-2026.xlsx
+++ b/SGC-CKN/Excel/6715dc33-90aa-4aee-8d9b-7a232d07818b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P17-154_D800_11-05-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>P17-154</t>
+    <t>P7-154</t>
   </si>
   <si>
     <t>Biên bản số</t>

--- a/SGC-CKN/Excel/6715dc33-90aa-4aee-8d9b-7a232d07818b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P17-154_D800_11-05-2026.xlsx
+++ b/SGC-CKN/Excel/6715dc33-90aa-4aee-8d9b-7a232d07818b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P17-154_D800_11-05-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="73">
   <si>
     <t>Dự án</t>
   </si>
@@ -38,10 +38,10 @@
     <t>P7-154</t>
   </si>
   <si>
-    <t>Biên bản số</t>
-  </si>
-  <si>
-    <t>M3-3.1.1.2.6</t>
+    <t>Tên Máy khoan</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Đường kính</t>
@@ -106,9 +106,6 @@
 10/03/2026</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -216,7 +213,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội, sỏi, sạn cát, đá khoảng, đa sắc, TT chặt đến rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">08:20
@@ -1256,24 +1253,24 @@
         <v>7.96</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="E12" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-6.5</v>
@@ -1291,24 +1288,24 @@
         <v>2.07</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="E13" s="15" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="15" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="13">
         <v>-8.5</v>
@@ -1326,24 +1323,24 @@
         <v>5.66</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="16" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="E14" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>42</v>
       </c>
       <c r="F14" s="16">
         <v>-16.7</v>
@@ -1361,24 +1358,24 @@
         <v>9.21</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="E15" s="21" t="s">
         <v>45</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>46</v>
       </c>
       <c r="F15" s="19">
         <v>-21</v>
@@ -1396,24 +1393,24 @@
         <v>0.8</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="23" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="E16" s="25" t="s">
         <v>49</v>
-      </c>
-      <c r="E16" s="25" t="s">
-        <v>50</v>
       </c>
       <c r="F16" s="23">
         <v>-25</v>
@@ -1431,24 +1428,24 @@
         <v>6.73</v>
       </c>
       <c r="K16" s="24" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17" s="28" t="s">
         <v>52</v>
-      </c>
-      <c r="D17" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>53</v>
       </c>
       <c r="F17" s="26">
         <v>-33.97</v>
@@ -1466,24 +1463,24 @@
         <v>3.75</v>
       </c>
       <c r="K17" s="27" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="31" t="s">
         <v>55</v>
-      </c>
-      <c r="D18" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>56</v>
       </c>
       <c r="F18" s="29">
         <v>-36.47</v>
@@ -1501,24 +1498,24 @@
         <v>1.7</v>
       </c>
       <c r="K18" s="30" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B19" s="32" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D19" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="34" t="s">
         <v>58</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>59</v>
       </c>
       <c r="F19" s="32">
         <v>-37.97</v>
@@ -1536,24 +1533,24 @@
         <v>7.54</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B20" s="35" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="37" t="s">
         <v>62</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>63</v>
       </c>
       <c r="F20" s="35">
         <v>-42.37</v>
@@ -1571,12 +1568,12 @@
         <v>1.44</v>
       </c>
       <c r="K20" s="36" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1682,31 +1679,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>71</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1746,7 +1743,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1775,7 +1772,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1804,7 +1801,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" s="16">
         <v>1</v>
@@ -1833,7 +1830,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D6" s="19">
         <v>1</v>
@@ -1862,7 +1859,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="23">
         <v>1</v>
@@ -1891,7 +1888,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" s="26">
         <v>1</v>
@@ -1920,7 +1917,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D9" s="29">
         <v>1</v>
@@ -1949,7 +1946,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" s="32">
         <v>1</v>
@@ -1978,7 +1975,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D11" s="35">
         <v>1</v>
@@ -2001,13 +1998,13 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="D12" s="40">
         <v>10</v>

--- a/SGC-CKN/Excel/6715dc33-90aa-4aee-8d9b-7a232d07818b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P17-154_D800_11-05-2026.xlsx
+++ b/SGC-CKN/Excel/6715dc33-90aa-4aee-8d9b-7a232d07818b_Phường_Hạc_Thành__tỉnh_Thanh_Hoá_P17-154_D800_11-05-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="72">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t/>
+    <t>SGCT-KCN0003</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">19:09
@@ -106,6 +106,9 @@
 10/03/2026</t>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
@@ -123,9 +126,6 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét xám trắng, xám xanh dẻo chảy</t>
-  </si>
-  <si>
     <t xml:space="preserve">21:00
 10/03/2026</t>
   </si>
@@ -151,7 +151,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, xám nâu TT chặt</t>
   </si>
   <si>
     <t xml:space="preserve">23:00
@@ -163,9 +163,6 @@
   </si>
   <si>
     <t>6</t>
-  </si>
-  <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">04:00
@@ -254,7 +251,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -336,11 +333,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color rgb="FF134E4A"/>
-      <sz val="10"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
@@ -353,7 +345,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -433,11 +425,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFBCFE8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99F6E4"/>
       </patternFill>
     </fill>
     <fill>
@@ -533,7 +520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -637,22 +624,13 @@
     <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1253,24 +1231,24 @@
         <v>7.96</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F12" s="9">
         <v>-6.5</v>
@@ -1288,18 +1266,18 @@
         <v>2.07</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>36</v>
@@ -1323,7 +1301,7 @@
         <v>5.66</v>
       </c>
       <c r="K13" s="14" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1358,7 +1336,7 @@
         <v>9.21</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -1393,198 +1371,198 @@
         <v>0.8</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="25" t="s">
+      <c r="E16" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="23">
+      <c r="F16" s="19">
         <v>-25</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="19">
         <v>-33.97</v>
       </c>
-      <c r="H16" s="23">
+      <c r="H16" s="19">
         <v>1.33</v>
       </c>
-      <c r="I16" s="23">
+      <c r="I16" s="19">
         <v>8.97</v>
       </c>
       <c r="J16" s="8">
         <v>6.73</v>
       </c>
-      <c r="K16" s="24" t="s">
-        <v>9</v>
+      <c r="K16" s="20" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="26" t="s">
+      <c r="A17" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="B17" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="27" t="s">
+      <c r="D17" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="26">
+      <c r="F17" s="23">
         <v>-33.97</v>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="23">
         <v>-36.47</v>
       </c>
-      <c r="H17" s="26">
+      <c r="H17" s="23">
         <v>0.67</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="23">
         <v>2.5</v>
       </c>
       <c r="J17" s="12">
         <v>3.75</v>
       </c>
-      <c r="K17" s="27" t="s">
-        <v>9</v>
+      <c r="K17" s="24" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="30" t="s">
+      <c r="D18" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="D18" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="29">
+      <c r="F18" s="26">
         <v>-36.47</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="26">
         <v>-37.97</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="26">
         <v>0.88</v>
       </c>
-      <c r="I18" s="29">
+      <c r="I18" s="26">
         <v>1.5</v>
       </c>
       <c r="J18" s="12">
         <v>1.7</v>
       </c>
-      <c r="K18" s="30" t="s">
-        <v>9</v>
+      <c r="K18" s="27" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="32" t="s">
+      <c r="A19" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B19" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="34" t="s">
+      <c r="E19" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="E19" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="32">
+      <c r="F19" s="29">
         <v>-37.97</v>
       </c>
-      <c r="G19" s="32">
+      <c r="G19" s="29">
         <v>-42.37</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H19" s="29">
         <v>0.58</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I19" s="29">
         <v>4.4</v>
       </c>
       <c r="J19" s="8">
         <v>7.54</v>
       </c>
-      <c r="K19" s="33" t="s">
+      <c r="K19" s="30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="32" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
+      <c r="B20" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="36" t="s">
+      <c r="D20" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="D20" s="37" t="s">
-        <v>58</v>
-      </c>
-      <c r="E20" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="35">
+      <c r="F20" s="32">
         <v>-42.37</v>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="32">
         <v>-43.57</v>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="32">
         <v>0.83</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="32">
         <v>1.2</v>
       </c>
       <c r="J20" s="12">
         <v>1.44</v>
       </c>
-      <c r="K20" s="36" t="s">
-        <v>9</v>
+      <c r="K20" s="33" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="38"/>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
+      <c r="A23" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
     </row>
     <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1666,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1679,31 +1657,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1743,7 +1721,7 @@
         <v>11</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
@@ -1772,7 +1750,7 @@
         <v>11</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D4" s="13">
         <v>1</v>
@@ -1833,22 +1811,22 @@
         <v>43</v>
       </c>
       <c r="D6" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="19">
         <v>-21</v>
       </c>
       <c r="F6" s="19">
-        <v>-25</v>
+        <v>-33.97</v>
       </c>
       <c r="G6" s="19">
-        <v>4.98</v>
+        <v>6.32</v>
       </c>
       <c r="H6" s="19">
-        <v>4</v>
-      </c>
-      <c r="I6" s="22">
-        <v>0.8</v>
+        <v>12.97</v>
+      </c>
+      <c r="I6" s="12">
+        <v>2.05</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1859,25 +1837,25 @@
         <v>11</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D7" s="23">
         <v>1</v>
       </c>
       <c r="E7" s="23">
-        <v>-25</v>
+        <v>-33.97</v>
       </c>
       <c r="F7" s="23">
-        <v>-33.97</v>
+        <v>-36.47</v>
       </c>
       <c r="G7" s="23">
-        <v>1.33</v>
+        <v>0.67</v>
       </c>
       <c r="H7" s="23">
-        <v>8.97</v>
-      </c>
-      <c r="I7" s="8">
-        <v>6.73</v>
+        <v>2.5</v>
+      </c>
+      <c r="I7" s="12">
+        <v>3.75</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1888,25 +1866,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D8" s="26">
         <v>1</v>
       </c>
       <c r="E8" s="26">
-        <v>-33.97</v>
+        <v>-36.47</v>
       </c>
       <c r="F8" s="26">
-        <v>-36.47</v>
+        <v>-37.97</v>
       </c>
       <c r="G8" s="26">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="H8" s="26">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="I8" s="12">
-        <v>3.75</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1917,25 +1895,25 @@
         <v>11</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D9" s="29">
         <v>1</v>
       </c>
       <c r="E9" s="29">
-        <v>-36.47</v>
+        <v>-37.97</v>
       </c>
       <c r="F9" s="29">
-        <v>-37.97</v>
+        <v>-42.37</v>
       </c>
       <c r="G9" s="29">
-        <v>0.88</v>
+        <v>0.58</v>
       </c>
       <c r="H9" s="29">
-        <v>1.5</v>
-      </c>
-      <c r="I9" s="12">
-        <v>1.7</v>
+        <v>4.4</v>
+      </c>
+      <c r="I9" s="8">
+        <v>7.54</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1946,82 +1924,53 @@
         <v>11</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="D10" s="32">
         <v>1</v>
       </c>
       <c r="E10" s="32">
-        <v>-37.97</v>
+        <v>-42.37</v>
       </c>
       <c r="F10" s="32">
-        <v>-42.37</v>
+        <v>-43.57</v>
       </c>
       <c r="G10" s="32">
-        <v>0.58</v>
+        <v>0.83</v>
       </c>
       <c r="H10" s="32">
-        <v>4.4</v>
-      </c>
-      <c r="I10" s="8">
-        <v>7.54</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="35">
+        <v>1.2</v>
+      </c>
+      <c r="I10" s="12">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="37">
         <v>10</v>
       </c>
-      <c r="B11" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="35">
-        <v>1</v>
-      </c>
-      <c r="E11" s="35">
-        <v>-42.37</v>
-      </c>
-      <c r="F11" s="35">
+      <c r="E11" s="37">
+        <v>0</v>
+      </c>
+      <c r="F11" s="37">
         <v>-43.57</v>
       </c>
-      <c r="G11" s="35">
-        <v>0.83</v>
-      </c>
-      <c r="H11" s="35">
-        <v>1.2</v>
-      </c>
-      <c r="I11" s="12">
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="B12" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="40">
-        <v>10</v>
-      </c>
-      <c r="E12" s="40">
-        <v>0</v>
-      </c>
-      <c r="F12" s="40">
-        <v>-43.57</v>
-      </c>
-      <c r="G12" s="40">
+      <c r="G11" s="37">
         <v>12.98</v>
       </c>
-      <c r="H12" s="40">
+      <c r="H11" s="37">
         <v>43.57</v>
       </c>
-      <c r="I12" s="40">
+      <c r="I11" s="37">
         <v>3.36</v>
       </c>
     </row>
